--- a/artfynd/A 35215-2025 artfynd.xlsx
+++ b/artfynd/A 35215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126017397</v>
+        <v>126017399</v>
       </c>
       <c r="B2" t="n">
-        <v>105396</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658931</v>
+        <v>658949</v>
       </c>
       <c r="R2" t="n">
-        <v>7210112</v>
+        <v>7210114</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126017400</v>
+        <v>126017394</v>
       </c>
       <c r="B3" t="n">
-        <v>78738</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658973</v>
+        <v>658983</v>
       </c>
       <c r="R3" t="n">
-        <v>7210056</v>
+        <v>7210065</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017399</v>
+        <v>126017400</v>
       </c>
       <c r="B4" t="n">
-        <v>82792</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658949</v>
+        <v>658973</v>
       </c>
       <c r="R4" t="n">
-        <v>7210114</v>
+        <v>7210056</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,7 +996,7 @@
         <v>126017396</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017394</v>
+        <v>126017391</v>
       </c>
       <c r="B6" t="n">
-        <v>92535</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>658983</v>
+        <v>658669</v>
       </c>
       <c r="R6" t="n">
-        <v>7210065</v>
+        <v>7210505</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,6 +1202,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126017397</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björksele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>658931</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7210112</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35215-2025 artfynd.xlsx
+++ b/artfynd/A 35215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017394</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017391</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017397</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>